--- a/artfynd/A 47336-2024 artfynd.xlsx
+++ b/artfynd/A 47336-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128012123</v>
       </c>
       <c r="B2" t="n">
-        <v>98479</v>
+        <v>98482</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 47336-2024 artfynd.xlsx
+++ b/artfynd/A 47336-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128012123</v>
       </c>
       <c r="B2" t="n">
-        <v>98482</v>
+        <v>98490</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 47336-2024 artfynd.xlsx
+++ b/artfynd/A 47336-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128012123</v>
       </c>
       <c r="B2" t="n">
-        <v>98490</v>
+        <v>98491</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 47336-2024 artfynd.xlsx
+++ b/artfynd/A 47336-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128012123</v>
       </c>
       <c r="B2" t="n">
-        <v>98491</v>
+        <v>98492</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 47336-2024 artfynd.xlsx
+++ b/artfynd/A 47336-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128012123</v>
       </c>
       <c r="B2" t="n">
-        <v>98492</v>
+        <v>98493</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 47336-2024 artfynd.xlsx
+++ b/artfynd/A 47336-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128012123</v>
       </c>
       <c r="B2" t="n">
-        <v>98493</v>
+        <v>98501</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 47336-2024 artfynd.xlsx
+++ b/artfynd/A 47336-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128012123</v>
       </c>
       <c r="B2" t="n">
-        <v>98501</v>
+        <v>98594</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 47336-2024 artfynd.xlsx
+++ b/artfynd/A 47336-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128012123</v>
       </c>
       <c r="B2" t="n">
-        <v>98594</v>
+        <v>98608</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 47336-2024 artfynd.xlsx
+++ b/artfynd/A 47336-2024 artfynd.xlsx
@@ -891,7 +891,7 @@
         <v>130154345</v>
       </c>
       <c r="B4" t="n">
-        <v>97702</v>
+        <v>97704</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>130154383</v>
       </c>
       <c r="B5" t="n">
-        <v>98748</v>
+        <v>98750</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 47336-2024 artfynd.xlsx
+++ b/artfynd/A 47336-2024 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>130154361</v>
       </c>
       <c r="B3" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>130154345</v>
       </c>
       <c r="B4" t="n">
-        <v>97704</v>
+        <v>97791</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>130154383</v>
       </c>
       <c r="B5" t="n">
-        <v>98750</v>
+        <v>98837</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 47336-2024 artfynd.xlsx
+++ b/artfynd/A 47336-2024 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>130154361</v>
       </c>
       <c r="B3" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>130154345</v>
       </c>
       <c r="B4" t="n">
-        <v>97791</v>
+        <v>97794</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>130154383</v>
       </c>
       <c r="B5" t="n">
-        <v>98837</v>
+        <v>98840</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 47336-2024 artfynd.xlsx
+++ b/artfynd/A 47336-2024 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>130154361</v>
       </c>
       <c r="B3" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>130154345</v>
       </c>
       <c r="B4" t="n">
-        <v>97794</v>
+        <v>97820</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>130154383</v>
       </c>
       <c r="B5" t="n">
-        <v>98840</v>
+        <v>98866</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 47336-2024 artfynd.xlsx
+++ b/artfynd/A 47336-2024 artfynd.xlsx
@@ -891,7 +891,7 @@
         <v>130154345</v>
       </c>
       <c r="B4" t="n">
-        <v>97820</v>
+        <v>97821</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>130154383</v>
       </c>
       <c r="B5" t="n">
-        <v>98866</v>
+        <v>98867</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 47336-2024 artfynd.xlsx
+++ b/artfynd/A 47336-2024 artfynd.xlsx
@@ -891,7 +891,7 @@
         <v>130154345</v>
       </c>
       <c r="B4" t="n">
-        <v>97821</v>
+        <v>97822</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>130154383</v>
       </c>
       <c r="B5" t="n">
-        <v>98867</v>
+        <v>98868</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 47336-2024 artfynd.xlsx
+++ b/artfynd/A 47336-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128012123</v>
+        <v>130154397</v>
       </c>
       <c r="B2" t="n">
-        <v>98608</v>
+        <v>97231</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,42 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219847</v>
+        <v>2869</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Norr 303, Dlr</t>
+          <t>Josmyran, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>403292</v>
+        <v>403343</v>
       </c>
       <c r="R2" t="n">
-        <v>6780660</v>
+        <v>6780701</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -748,17 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Enstaka</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -767,24 +754,18 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Barrblandsumpskog</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Henrik Liliedahl</t>
+          <t>Elliot Örjes</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Henrik Liliedahl</t>
+          <t>Niklas Rehn</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -794,11 +775,11 @@
         <v>130154361</v>
       </c>
       <c r="B3" t="n">
-        <v>79209</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -822,7 +803,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Malung-Sälen Västra Sälen 7:374, Dlr</t>
+          <t>Josmyran, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
@@ -888,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130154345</v>
+        <v>130154381</v>
       </c>
       <c r="B4" t="n">
-        <v>97822</v>
+        <v>99035</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -899,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>219790</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -923,14 +904,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Malung-Sälen Västra Sälen 7:390, Dlr</t>
+          <t>Josmyran, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>403345</v>
+        <v>403386</v>
       </c>
       <c r="R4" t="n">
-        <v>6780731</v>
+        <v>6780742</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -990,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130154383</v>
+        <v>130154382</v>
       </c>
       <c r="B5" t="n">
-        <v>98868</v>
+        <v>99035</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1025,14 +1006,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Malung-Sälen Västra Sälen 7:353, Dlr</t>
+          <t>Josmyran, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>403338</v>
+        <v>403375</v>
       </c>
       <c r="R5" t="n">
-        <v>6780717</v>
+        <v>6780751</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1089,6 +1070,530 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>130154383</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Josmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>403338</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6780717</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Elliot Örjes</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>130154384</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Josmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>403351</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6780703</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Elliot Örjes</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>130154385</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Josmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>403363</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6780704</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Elliot Örjes</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128012123</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99142</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Norr 303, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>403292</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6780660</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Barrblandsumpskog</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Henrik Liliedahl</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Henrik Liliedahl</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>130154345</v>
+      </c>
+      <c r="B10" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Josmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>403345</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6780731</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Elliot Örjes</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 47336-2024 artfynd.xlsx
+++ b/artfynd/A 47336-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130154397</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130154361</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -968,6 +983,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130154381</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1070,6 +1090,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130154382</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1172,6 +1197,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130154383</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1274,6 +1304,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130154384</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1376,6 +1411,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130154385</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1492,6 +1532,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128012123</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1594,8 +1639,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130154345</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>